--- a/MOTION&CABLING/CSC-Cabling-Sizing-Config.xlsx
+++ b/MOTION&CABLING/CSC-Cabling-Sizing-Config.xlsx
@@ -1,39 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HALS-DOCUMENTATION\GitHub-CABLING&amp;MOTION\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\NFSROBOT\HALS-Documentation\GitHub-MOTION (Electronics-Motors)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{432465DA-0385-4017-B4EB-E582398D0449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECC65252-A205-4603-BCF2-0902BCC76E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="3315" windowWidth="16365" windowHeight="11295" activeTab="1" xr2:uid="{C0FF467A-F343-43B1-956E-06FD2F343560}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="19665" windowHeight="11100" xr2:uid="{B16F982D-C3E3-4EB6-A776-715ADD429CBA}"/>
   </bookViews>
   <sheets>
     <sheet name="CSC; Cabling-Sizing-Config." sheetId="1" r:id="rId1"/>
-    <sheet name="CSC-BOM" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CSC-BOM'!$A$3:$F$17</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'CSC; Cabling-Sizing-Config.'!$B$83:$K$119</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -44,22 +50,82 @@
     <t>CSC001</t>
   </si>
   <si>
+    <t>Time to consider the sizing and configuration of cabling.
+Starting point: 
+1/ the Arduino-CNCShield, so one central "box" 
+2/ endstops for Z and R and PHI, connected in series, but in NC config.
+3/ Cabling for motors and endstops shielded to minimize interference with Mic cabling etc. The shields connected to safety ground (Dutch: Randaarde)
+4/ Cable chain over casing rotating drive to connect the cabling to foot, with rotation of at least 0 to 180 and 0 to -180 degree without issues.
+5/ Loudspeaker cabling, a Cordial CLS425, part of BASE, length 7m.
+6/ Mic cabling not closely together with motor/endstop cabling.</t>
+  </si>
+  <si>
     <t>CSC002</t>
   </si>
   <si>
+    <t>On Z-axis and R-axis there will be endstops, so cabling also for these.
+Cabling for motors.</t>
+  </si>
+  <si>
     <t>CSC003</t>
   </si>
   <si>
+    <t>Mic cable length needed  at least 5m, better 10m, plus tules for passing through tubing.</t>
+  </si>
+  <si>
     <t>CSC004</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">2 x 0.5mm2 shielded for endstops, total of 15m, bending radius ~57
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Addendum: use the endstop pcbs as they alteady hold caps and resistors and mounted in box so at arduino side to further reduce noise interferences. The cabling is ordered and received. In a next version of the NFSROBOT i will replace the endstop cabling with Sommer Cable Cicada SO-D14, being less weight, more flexible, 2x 0.14mm2 and still shielded.</t>
+    </r>
+  </si>
+  <si>
     <t>CSC005</t>
   </si>
   <si>
+    <t>4x0.75mm2 shielded for motors, total of 11m bending radius ~75mm</t>
+  </si>
+  <si>
     <t>CSC006</t>
   </si>
   <si>
+    <r>
+      <t xml:space="preserve">Cable chain for cabling from arm assy to foot. On top of drive casing, length ~ 1000 mm will do. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Addendum: Perhaps an RBR can be put in place, it may further reduce the cable-length needed , at least what preliminary investigations show.</t>
+    </r>
+  </si>
+  <si>
     <t>CSC007</t>
+  </si>
+  <si>
+    <t>To bundle cabling of Z-axis along Arm, I have chosen for horizontal cablechain. It only involves the z-axis motor and endstop cabling.  
+Note: Mic-cable not together with motor-endstop cabling. Checklist C010. Done</t>
   </si>
   <si>
     <t>CSC008</t>
@@ -229,164 +295,12 @@
   <si>
     <t xml:space="preserve">Helukabel F-CY-JZ 4G0.75mm² stuurstroomkabel afgeschermd </t>
   </si>
-  <si>
-    <t>Mic cable length needed is 10m, plus tules for passing through tubing. With Neutrik XLR connectors, and the mic side slightly filed to fit through the Mic-beam interior diameter of ~ 20mm. This XLR then fixed with gaffer-tape around it to make it stick-fit.</t>
-  </si>
-  <si>
-    <t>Time to consider the sizing and configuration of cabling.
-Starting point: 
-1/ the BTT SKR3EZ with grblHAL firmware, so one central "box" 
-2/ Two endstops for Z and R  connected in series, in NC (Normally Closed) configuration. One endstop for PHI also in NC configuration.
-3/ Cabling for motors and endstops shielded to minimize interference with Mic cabling etc. The shields connected to safety ground (Dutch: Randaarde)
-4/ Cable chain spiral on top of rotating drive to connect the cabling to foot, with rotation of at least 0 to 180 and 0 to -180 degree without issues.
-5/ Loudspeaker cabling, a Cordial CLS425, part of BASE, length 7m.
-6/ Mic cabling not closely together with motor/endstop cabling.</t>
-  </si>
-  <si>
-    <t>For endstops cabling 2 x 0.5mm2 shielded, total of 15m, bending radius ~57 mm. See also table for length calculation. To connect the endstops with the calbe a rather long length is stripped and the wire twisted so smaller bending radii are possible. The shield is left to touch the alu profiles.</t>
-  </si>
-  <si>
-    <t>For the motor 4x0.75mm2 shielded , total of 11m bending radius ~75mm. To connect to motor a endcap is modelled to be 3D printed, to assure a firm mounting of calble to motor.</t>
-  </si>
-  <si>
-    <t>Cable chain for cabling from arm assy to foot. On top of drive casing, length ~ 1000 mm will do. I could get a 30x15mm (interior opening) cable chain. To keep the wiring sort of nica, I used foam pads to fill on the inside to keep the wires pressed againste the outside, so a more even bending occurs.</t>
-  </si>
-  <si>
-    <t>To bundle cabling of Z-axis along Arm, I have chosen for horizontal cablechain 20x10mm inside dimensions. It only involves the z-axis motor and endstop cabling.  
-Note: Mic-cable not closely together with motor-endstop cabling. Checklist C010. Done I placed it on top of the cable chains mounted with velcro bands, so it can easily be dismounted, and keeps a bit of distance from the motor cabling.</t>
-  </si>
-  <si>
-    <t>As an alternative a 3D printable microswitch holder is designed.</t>
-  </si>
-  <si>
-    <t>For the connectors I decided for GX16-4 for motor cabling, and GX12-2 for endstop cabling. Primarely for cost reasons, more modern alternatives are better but cost several times more.</t>
-  </si>
-  <si>
-    <t>Th shielding is connected to the connector (both plug and chassis) and in the controller the shielding is connected to safety ground of the 24V power supply.</t>
-  </si>
-  <si>
-    <t>CSC022</t>
-  </si>
-  <si>
-    <t>By accident I made an error in connecting the PHI-Axis cable to plug on controller side. In the drawing belwo this is noted as ISSUE. Do not copy ;-)</t>
-  </si>
-  <si>
-    <t>As the Z-axis assy as a main module is ment to be dismountable, on the gantry there is a junction with GX16-4 and GX12-2 connector (Plug and Chassis) are needed.</t>
-  </si>
-  <si>
-    <t>CSC023</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Part ID</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Buy/Make</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Buy</t>
-  </si>
-  <si>
-    <t>Make</t>
-  </si>
-  <si>
-    <t>BOM for the HALS-Mechatronics CSC</t>
-  </si>
-  <si>
-    <t>CSC</t>
-  </si>
-  <si>
-    <t>NEMA17-Endcap-Cabling</t>
-  </si>
-  <si>
-    <t>Cable-Chain-Z-Arm-10x20mm-1.5m</t>
-  </si>
-  <si>
-    <t>Typically sold in length of 1 m so then purchase 2x1m.</t>
-  </si>
-  <si>
-    <t>Cable-Chain-Spiral-Hub-15x30mm - 1m</t>
-  </si>
-  <si>
-    <t>Countersunk screws 3.2mmx12mm</t>
-  </si>
-  <si>
-    <t>type Parker or metal screw ; to mount the ends of cable chain to the structure.</t>
-  </si>
-  <si>
-    <t>microswitch</t>
-  </si>
-  <si>
-    <t>GX16-4 plug and chassis</t>
-  </si>
-  <si>
-    <t>GX12-2 plug and chassis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endstop cabling: 2x 0.25 (0.5)mm2 shielded </t>
-  </si>
-  <si>
-    <t>15 m , see table on other tab</t>
-  </si>
-  <si>
-    <t>11 m , see table on other tab</t>
-  </si>
-  <si>
-    <t>XLR-Cable-Male-Female-10m</t>
-  </si>
-  <si>
-    <t>Microphone cable, Neutrik XLR plugs</t>
-  </si>
-  <si>
-    <t>3D printed using PETG (Rapid PETG)</t>
-  </si>
-  <si>
-    <t>M3x12 bolt plus nut</t>
-  </si>
-  <si>
-    <t>CS024</t>
-  </si>
-  <si>
-    <t>The cabling of endstops fits in the slot of the V-Slot profiles, some gaffer tape or a piece of stripped outer sleeve can be used to keep it in place.</t>
-  </si>
-  <si>
-    <t>As explained by the grblHAL support for the BTT SKR3 EZ , the pins for Cycle Start, Feed Hold and Reset are connected to ground. These are specific for CNC. A separate wiring scheme is shown below.</t>
-  </si>
-  <si>
-    <t>I glued these to the sturcture, except for the one in the rotating drive. That one is clamped</t>
-  </si>
-  <si>
-    <t>To clamp the endcap on the rear of the motor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor cabling: 4x0.75mm2 shielded </t>
-  </si>
-  <si>
-    <t>A separate 3D model of the calbing harness is made to depict the cabling and cable chain assembling. Picture of the endstop connection etc  will be added. The stripped parts of the cables is not shown in 3D.</t>
-  </si>
-  <si>
-    <t>Controller-Case-24v-mounts</t>
-  </si>
-  <si>
-    <t>3D printed using PETG (Rapid PETG) (several parts in 1 file)</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,23 +317,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <u/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -433,7 +342,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -588,94 +497,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -719,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -731,13 +558,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -776,7 +596,7 @@
         <xdr:cNvPr id="2" name="Afbeelding 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCE0E448-4E04-46C8-A381-86A95351D5E5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{147B4299-4E36-40C9-A96C-AEE0828D586C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -839,7 +659,7 @@
             <xdr14:cNvPr id="3" name="Inkt 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{850E3B5D-BC25-4880-B768-E587948D70F0}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC106B9A-052E-430C-AB22-11CD2B33E8E8}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -904,7 +724,7 @@
             <xdr14:cNvPr id="4" name="Inkt 3">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8FC0CFB-5406-49BB-94C0-E66144B25D88}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAA88B8E-AA02-453E-9791-7A9D460AD56D}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -969,7 +789,7 @@
             <xdr14:cNvPr id="5" name="Inkt 4">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4632B9B5-21D8-4F83-B0D8-EF13194CD66D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{874CB012-F45B-4743-A5B2-1FCD749A6C6B}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1034,7 +854,7 @@
             <xdr14:cNvPr id="6" name="Inkt 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{604EC5D9-DA94-44AF-8457-BCB7F610E85F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DEF52E5-019E-4481-9113-D449B9AC62AE}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1099,7 +919,7 @@
             <xdr14:cNvPr id="7" name="Inkt 6">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA4E88A0-7AA8-4B2D-AC58-0B555F32B67F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAC65D64-67E0-41FF-AB5B-6FF5A658C442}"/>
                 </a:ext>
               </a:extLst>
             </xdr14:cNvPr>
@@ -1162,7 +982,7 @@
         <xdr:cNvPr id="8" name="Afbeelding 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EB07800-B717-4831-BA4C-194996B8605E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C24F01BA-A248-443E-83B5-5929AA58C29F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1214,7 +1034,7 @@
         <xdr:cNvPr id="9" name="Afbeelding 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D42CEAE1-997E-4AF8-887E-7C3A157AFCE2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8079C0C5-F610-4AA1-8DB1-00D7A2DD59DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1266,7 +1086,7 @@
         <xdr:cNvPr id="10" name="Afbeelding 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA441BCF-7D0C-4D73-A2EE-ABDDC0E0422A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453C3EF8-6FC2-4FE7-B9B1-B3EBAFAF2EDF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1319,7 +1139,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-05-03T09:04:09.821"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-16T18:10:30.896"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1347,7 +1167,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-05-03T09:04:09.822"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-16T18:10:30.897"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1375,7 +1195,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-05-03T09:04:09.823"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-16T18:10:30.898"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1403,7 +1223,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-05-03T09:04:09.824"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-16T18:10:30.899"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1431,7 +1251,7 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-05-03T09:04:09.825"/>
+      <inkml:timestamp xml:id="ts0" timeString="2026-04-16T18:10:30.900"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -1705,7 +1525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A5E5DC1-9820-4529-8686-9A20489EAFAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EC14D90-F28D-401F-B994-89E7FA4E7C63}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1726,132 +1546,132 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="150" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U17" s="5"/>
       <c r="V17" s="5"/>
@@ -1859,10 +1679,10 @@
     </row>
     <row r="18" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
@@ -1870,10 +1690,10 @@
     </row>
     <row r="19" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="U19" s="5"/>
       <c r="V19" s="5"/>
@@ -1881,13 +1701,11 @@
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>63</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B20" s="4"/>
       <c r="D20" s="6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1895,7 +1713,7 @@
       <c r="H20" s="8"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -1910,22 +1728,20 @@
       <c r="W20" s="5"/>
       <c r="X20" s="5"/>
     </row>
-    <row r="21" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B21" s="4"/>
       <c r="D21" s="12"/>
       <c r="E21" s="13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="T21" s="11"/>
@@ -1934,15 +1750,13 @@
       <c r="W21" s="5"/>
       <c r="X21" s="5"/>
     </row>
-    <row r="22" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>65</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B22" s="4"/>
       <c r="D22" s="13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E22" s="15">
         <v>2</v>
@@ -1954,22 +1768,18 @@
         <v>0</v>
       </c>
       <c r="J22" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="U22" s="5"/>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
     </row>
-    <row r="23" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>67</v>
-      </c>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+      <c r="B23" s="4"/>
       <c r="D23" s="16" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E23" s="17">
         <v>2</v>
@@ -1981,22 +1791,18 @@
         <v>0</v>
       </c>
       <c r="J23" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q23" s="14"/>
       <c r="U23" s="5"/>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
     </row>
-    <row r="24" spans="1:24" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>98</v>
-      </c>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="3"/>
+      <c r="B24" s="4"/>
       <c r="D24" s="13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E24" s="15">
         <v>2</v>
@@ -2008,19 +1814,15 @@
         <v>2</v>
       </c>
       <c r="J24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q24" s="14"/>
     </row>
-    <row r="25" spans="1:24" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>102</v>
-      </c>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="4"/>
       <c r="D25" s="18" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="E25" s="19">
         <f>SUM(E22:E24)</f>
@@ -2039,24 +1841,20 @@
         <v>13</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="14"/>
       <c r="U25" s="5"/>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
     </row>
-    <row r="26" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>97</v>
-      </c>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="3"/>
+      <c r="B26" s="4"/>
       <c r="D26" s="20"/>
       <c r="E26" s="5"/>
       <c r="F26" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G26" s="22"/>
       <c r="H26" s="23">
@@ -2064,10 +1862,10 @@
         <v>15</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J26" s="24" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Q26" s="14"/>
       <c r="U26" s="5"/>
@@ -2090,7 +1888,7 @@
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="D28" s="6" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E28" s="25"/>
       <c r="F28" s="25"/>
@@ -2108,13 +1906,13 @@
       <c r="B29" s="4"/>
       <c r="D29" s="12"/>
       <c r="E29" s="13" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q29" s="14"/>
       <c r="U29" s="5"/>
@@ -2126,7 +1924,7 @@
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="D30" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E30" s="15">
         <v>3</v>
@@ -2138,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Q30" s="14"/>
       <c r="U30" s="5"/>
@@ -2149,7 +1947,7 @@
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="D31" s="13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E31" s="15">
         <v>2</v>
@@ -2161,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="U31" s="5"/>
@@ -2172,7 +1970,7 @@
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="D32" s="13" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E32" s="15">
         <v>0</v>
@@ -2184,13 +1982,13 @@
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="Q32" s="14"/>
     </row>
     <row r="33" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D33" s="26" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E33" s="15">
         <f>SUM(E30:E32)</f>
@@ -2209,7 +2007,7 @@
         <v>9</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="T33" s="27"/>
@@ -2218,7 +2016,7 @@
       <c r="D34" s="28"/>
       <c r="E34" s="29"/>
       <c r="F34" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G34" s="22"/>
       <c r="H34" s="23">
@@ -2226,10 +2024,10 @@
         <v>11</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J34" s="30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K34" s="31"/>
       <c r="L34" s="31"/>
@@ -2247,302 +2045,4 @@
   </colBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23784A58-542E-4EDD-A20D-768FC539E111}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="43.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="83.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="37"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>74</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" s="41" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="41">
-        <v>3</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="41" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="41">
-        <v>6</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="13">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="13">
-        <v>1</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="13">
-        <v>8</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="13">
-        <v>5</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="13">
-        <v>4</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" s="13">
-        <v>4</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" s="13">
-        <v>15</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="13">
-        <v>11</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="13">
-        <v>1</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="13">
-        <v>1</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:F17" xr:uid="{23784A58-542E-4EDD-A20D-768FC539E111}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>